--- a/outputs/tables/tabla_07_cobertura_natural.xlsx
+++ b/outputs/tables/tabla_07_cobertura_natural.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cobertura_natural" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,47 +444,27 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>margen_pct_con_hedge</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>margen_pct_sin_hedge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>amortiguacion_pp</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>pct_importado</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pct_nacional</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ingreso_cop</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>costo_total_cop</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>margen_cop</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>margen_pct</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>costo_total_ajustado</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>margen_cop_ajustado</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>margen_pct_ajustado</t>
+          <t>fx_relativo</t>
         </is>
       </c>
     </row>
@@ -506,38 +486,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F2" t="n">
+        <v>26.58268479167631</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24.68201007640215</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.900674715274153</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.25</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H2" t="n">
-        <v>13174.81311303553</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8135.412926987981</v>
-      </c>
       <c r="J2" t="n">
-        <v>5039.400186047544</v>
-      </c>
-      <c r="K2" t="n">
-        <v>38.25025936088172</v>
-      </c>
-      <c r="L2" t="n">
-        <v>8135.412926987981</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5039.400186047544</v>
-      </c>
-      <c r="N2" t="n">
-        <v>38.25025936088172</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="3">
@@ -558,38 +526,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F3" t="n">
+        <v>32.30822516808272</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32.30822516808272</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.25</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H3" t="n">
-        <v>14492.29442433908</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8135.412926987981</v>
-      </c>
       <c r="J3" t="n">
-        <v>6356.8814973511</v>
-      </c>
-      <c r="K3" t="n">
-        <v>43.86387214625613</v>
-      </c>
-      <c r="L3" t="n">
-        <v>8333.035123683514</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6159.259300655567</v>
-      </c>
-      <c r="N3" t="n">
-        <v>42.50023578261977</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -610,38 +566,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F4" t="n">
+        <v>37.8796083196522</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.72910834744502</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.849500027792821</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.25</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11198.5911460802</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8135.412926987981</v>
-      </c>
       <c r="J4" t="n">
-        <v>3063.178219092215</v>
-      </c>
-      <c r="K4" t="n">
-        <v>27.35324630691968</v>
-      </c>
-      <c r="L4" t="n">
-        <v>7838.979631944682</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3359.611514135514</v>
-      </c>
-      <c r="N4" t="n">
-        <v>30.00030513044909</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="5">
@@ -662,38 +606,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F5" t="n">
+        <v>25.88808149609869</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24.0370712496845</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.851010246414191</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.25</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H5" t="n">
-        <v>13174.81311303553</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9069.123925321315</v>
-      </c>
       <c r="J5" t="n">
-        <v>4105.68918771421</v>
-      </c>
-      <c r="K5" t="n">
-        <v>31.16316833103255</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9069.123925321315</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4105.68918771421</v>
-      </c>
-      <c r="N5" t="n">
-        <v>31.16316833103255</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="6">
@@ -714,38 +646,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F6" t="n">
+        <v>31.55407465507075</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31.55407465507075</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.25</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>14492.29442433908</v>
-      </c>
-      <c r="I6" t="n">
-        <v>9069.123925321315</v>
-      </c>
       <c r="J6" t="n">
-        <v>5423.170499017766</v>
-      </c>
-      <c r="K6" t="n">
-        <v>37.42106211912051</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9266.746122016848</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5225.548302322233</v>
-      </c>
-      <c r="N6" t="n">
-        <v>36.05742575548415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -766,38 +686,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F7" t="n">
+        <v>37.09873859383735</v>
+      </c>
+      <c r="G7" t="n">
+        <v>38.910112076936</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1.811373483098649</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.25</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>11198.5911460802</v>
-      </c>
-      <c r="I7" t="n">
-        <v>9069.123925321315</v>
-      </c>
       <c r="J7" t="n">
-        <v>2129.467220758881</v>
-      </c>
-      <c r="K7" t="n">
-        <v>19.01549215415594</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8772.690630278015</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2425.900515802181</v>
-      </c>
-      <c r="N7" t="n">
-        <v>21.66255097768535</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="8">
@@ -818,38 +726,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F8" t="n">
+        <v>0.4968795904052152</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.8483810268463722</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.345260617251587</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.15</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H8" t="n">
-        <v>362.307360608477</v>
-      </c>
-      <c r="I8" t="n">
-        <v>447.9094755317528</v>
-      </c>
       <c r="J8" t="n">
-        <v>-85.60211492327585</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-23.62693233157378</v>
-      </c>
-      <c r="L8" t="n">
-        <v>447.9094755317528</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-85.60211492327585</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-23.62693233157378</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="9">
@@ -870,38 +766,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F9" t="n">
+        <v>8.251728960273894</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.251728960273894</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.15</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H9" t="n">
-        <v>398.5380966693247</v>
-      </c>
-      <c r="I9" t="n">
-        <v>447.9094755317528</v>
-      </c>
       <c r="J9" t="n">
-        <v>-49.37137886242812</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-12.3881203014307</v>
-      </c>
-      <c r="L9" t="n">
-        <v>451.1702417772291</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-52.63214510790442</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-13.20630211961252</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -922,38 +806,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F10" t="n">
+        <v>16.03179183369398</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17.3814263248576</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.34963449116362</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.15</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H10" t="n">
-        <v>307.9612565172054</v>
-      </c>
-      <c r="I10" t="n">
-        <v>447.9094755317528</v>
-      </c>
       <c r="J10" t="n">
-        <v>-139.9482190145474</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-45.44344980185151</v>
-      </c>
-      <c r="L10" t="n">
-        <v>443.0183261635384</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-135.057069646333</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-43.85521450773387</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="11">
@@ -974,38 +846,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F11" t="n">
+        <v>0.4653352841673579</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.7945217188087744</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.259857002976132</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.15</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H11" t="n">
-        <v>362.307360608477</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1381.620473865086</v>
-      </c>
       <c r="J11" t="n">
-        <v>-1019.313113256609</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-281.3393334169983</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1381.620473865086</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-1019.313113256609</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-281.3393334169983</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="12">
@@ -1026,38 +886,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F12" t="n">
+        <v>7.774978348693535</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.774978348693535</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.15</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H12" t="n">
-        <v>398.5380966693247</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1381.620473865086</v>
-      </c>
       <c r="J12" t="n">
-        <v>-983.0823771957616</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-246.6721212881802</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1384.881240110562</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-986.3431434412378</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-247.490303106362</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1078,38 +926,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F13" t="n">
+        <v>15.19849224488346</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16.47797550914757</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.279483264264112</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.15</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H13" t="n">
-        <v>307.9612565172054</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1381.620473865086</v>
-      </c>
       <c r="J13" t="n">
-        <v>-1073.659217347881</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-348.6345099023509</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1376.729324496872</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-1068.768067979667</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-347.0462746082333</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="14">
@@ -1130,38 +966,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F14" t="n">
+        <v>11.66771770402581</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.178611847642241</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.489105856383572</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.3</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4940.554917388322</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3194.85800959966</v>
-      </c>
       <c r="J14" t="n">
-        <v>1745.696907788662</v>
-      </c>
-      <c r="K14" t="n">
-        <v>35.33402496235125</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3194.85800959966</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1745.696907788662</v>
-      </c>
-      <c r="N14" t="n">
-        <v>35.33402496235125</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="15">
@@ -1182,38 +1006,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F15" t="n">
+        <v>17.67727395045441</v>
+      </c>
+      <c r="G15" t="n">
+        <v>17.67727395045441</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.3</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5434.610409127155</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3194.85800959966</v>
-      </c>
       <c r="J15" t="n">
-        <v>2239.752399527496</v>
-      </c>
-      <c r="K15" t="n">
-        <v>41.21274996577388</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3283.78799811265</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2150.822411014506</v>
-      </c>
-      <c r="N15" t="n">
-        <v>39.57638632941025</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1234,38 +1046,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F16" t="n">
+        <v>23.65098675948716</v>
+      </c>
+      <c r="G16" t="n">
+        <v>26.12524657628369</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-2.474259816796533</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.3</v>
       </c>
-      <c r="G16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4199.471679780074</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3194.85800959966</v>
-      </c>
       <c r="J16" t="n">
-        <v>1004.613670180414</v>
-      </c>
-      <c r="K16" t="n">
-        <v>23.92238230864854</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3061.463026830175</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1138.008652949899</v>
-      </c>
-      <c r="N16" t="n">
-        <v>27.09885289688384</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="17">
@@ -1286,38 +1086,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F17" t="n">
+        <v>8.213903807870611</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.461609435434119</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.752294372436492</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.3</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4940.554917388322</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4128.569007932993</v>
-      </c>
       <c r="J17" t="n">
-        <v>811.9859094553285</v>
-      </c>
-      <c r="K17" t="n">
-        <v>16.43511554942012</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4128.569007932993</v>
-      </c>
-      <c r="M17" t="n">
-        <v>811.9859094553285</v>
-      </c>
-      <c r="N17" t="n">
-        <v>16.43511554942012</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="18">
@@ -1338,38 +1126,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F18" t="n">
+        <v>12.82262311832864</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12.82262311832864</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.3</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5434.610409127155</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4128.569007932993</v>
-      </c>
       <c r="J18" t="n">
-        <v>1306.041401194162</v>
-      </c>
-      <c r="K18" t="n">
-        <v>24.03192322674558</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4217.498996445984</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1217.111412681172</v>
-      </c>
-      <c r="N18" t="n">
-        <v>22.39555959038194</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1390,38 +1166,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F19" t="n">
+        <v>17.69003227520679</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19.54068385526488</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1.850651580058088</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.3</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4199.471679780074</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4128.569007932993</v>
-      </c>
       <c r="J19" t="n">
-        <v>70.90267184708046</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.688371234611912</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3995.174025163508</v>
-      </c>
-      <c r="M19" t="n">
-        <v>204.2976546165655</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.864841822847215</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="20">
@@ -1442,38 +1206,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F20" t="n">
+        <v>-0.008320382529565275</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.530445629629771</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.522125247100206</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.3</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H20" t="n">
-        <v>10292.822744559</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6406.218705902068</v>
-      </c>
       <c r="J20" t="n">
-        <v>3886.604038656936</v>
-      </c>
-      <c r="K20" t="n">
-        <v>37.76033198192862</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6406.218705902068</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3886.604038656936</v>
-      </c>
-      <c r="N20" t="n">
-        <v>37.76033198192862</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="21">
@@ -1494,38 +1246,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F21" t="n">
+        <v>3.761340012334498</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.761340012334498</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.3</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H21" t="n">
-        <v>11322.10501901491</v>
-      </c>
-      <c r="I21" t="n">
-        <v>6406.218705902068</v>
-      </c>
       <c r="J21" t="n">
-        <v>4915.886313112839</v>
-      </c>
-      <c r="K21" t="n">
-        <v>43.41848361993512</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6591.48951530413</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4730.615503710777</v>
-      </c>
-      <c r="N21" t="n">
-        <v>41.78211998357148</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1546,38 +1286,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F22" t="n">
+        <v>7.896906031556466</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.56677779440381</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.669871762847344</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.3</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>8748.899332875153</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6406.218705902068</v>
-      </c>
       <c r="J22" t="n">
-        <v>2342.680626973085</v>
-      </c>
-      <c r="K22" t="n">
-        <v>26.77686115521013</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6128.312491798974</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2620.586841076179</v>
-      </c>
-      <c r="N22" t="n">
-        <v>29.95333174344543</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="23">
@@ -1598,38 +1326,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F23" t="n">
+        <v>-0.008320382529565275</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.530445629629771</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.522125247100206</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.3</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H23" t="n">
-        <v>10292.822744559</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7339.929704235402</v>
-      </c>
       <c r="J23" t="n">
-        <v>2952.893040323602</v>
-      </c>
-      <c r="K23" t="n">
-        <v>28.68885546372166</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7339.929704235402</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2952.893040323602</v>
-      </c>
-      <c r="N23" t="n">
-        <v>28.68885546372166</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="24">
@@ -1650,38 +1366,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F24" t="n">
+        <v>3.761340012334498</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.761340012334498</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.3</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>11322.10501901491</v>
-      </c>
-      <c r="I24" t="n">
-        <v>7339.929704235402</v>
-      </c>
       <c r="J24" t="n">
-        <v>3982.175314779505</v>
-      </c>
-      <c r="K24" t="n">
-        <v>35.17168678520153</v>
-      </c>
-      <c r="L24" t="n">
-        <v>7525.200513637464</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3796.904505377443</v>
-      </c>
-      <c r="N24" t="n">
-        <v>33.5353231488379</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1702,38 +1406,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F25" t="n">
+        <v>7.896906031556466</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.56677779440381</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.669871762847344</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.3</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8748.899332875153</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7339.929704235402</v>
-      </c>
       <c r="J25" t="n">
-        <v>1408.969628639751</v>
-      </c>
-      <c r="K25" t="n">
-        <v>16.10453583967254</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7062.023490132308</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1686.875842742845</v>
-      </c>
-      <c r="N25" t="n">
-        <v>19.28100642790784</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="26">
@@ -1754,38 +1446,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F26" t="n">
+        <v>37.00891061577138</v>
+      </c>
+      <c r="G26" t="n">
+        <v>32.60951346591461</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.399397149856775</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.65</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H26" t="n">
-        <v>115279.6147390609</v>
-      </c>
-      <c r="I26" t="n">
-        <v>69398.29390260318</v>
-      </c>
       <c r="J26" t="n">
-        <v>45881.32083645767</v>
-      </c>
-      <c r="K26" t="n">
-        <v>39.80002964124363</v>
-      </c>
-      <c r="L26" t="n">
-        <v>69398.29390260318</v>
-      </c>
-      <c r="M26" t="n">
-        <v>45881.32083645767</v>
-      </c>
-      <c r="N26" t="n">
-        <v>39.80002964124363</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="27">
@@ -1806,38 +1486,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F27" t="n">
+        <v>39.39120508247916</v>
+      </c>
+      <c r="G27" t="n">
+        <v>39.39120508247917</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-7.105427357601002e-15</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.65</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H27" t="n">
-        <v>126807.576212967</v>
-      </c>
-      <c r="I27" t="n">
-        <v>69398.29390260318</v>
-      </c>
       <c r="J27" t="n">
-        <v>57409.28231036378</v>
-      </c>
-      <c r="K27" t="n">
-        <v>45.2727542193124</v>
-      </c>
-      <c r="L27" t="n">
-        <v>73894.19887742656</v>
-      </c>
-      <c r="M27" t="n">
-        <v>52913.3773355404</v>
-      </c>
-      <c r="N27" t="n">
-        <v>41.72729967385784</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1858,38 +1526,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F28" t="n">
+        <v>41.70758293837785</v>
+      </c>
+      <c r="G28" t="n">
+        <v>45.98525149683908</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-4.277668558461237</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.65</v>
       </c>
-      <c r="G28" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H28" t="n">
-        <v>97987.67252820171</v>
-      </c>
-      <c r="I28" t="n">
-        <v>69398.29390260318</v>
-      </c>
       <c r="J28" t="n">
-        <v>28589.37862559853</v>
-      </c>
-      <c r="K28" t="n">
-        <v>29.17650546028661</v>
-      </c>
-      <c r="L28" t="n">
-        <v>62654.43644036812</v>
-      </c>
-      <c r="M28" t="n">
-        <v>35333.23608783359</v>
-      </c>
-      <c r="N28" t="n">
-        <v>36.05885840146307</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="29">
@@ -1910,38 +1566,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F29" t="n">
+        <v>36.55097148965275</v>
+      </c>
+      <c r="G29" t="n">
+        <v>32.20601139435211</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.344960095300635</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.65</v>
       </c>
-      <c r="G29" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H29" t="n">
-        <v>115279.6147390609</v>
-      </c>
-      <c r="I29" t="n">
-        <v>70332.00490093652</v>
-      </c>
       <c r="J29" t="n">
-        <v>44947.60983812434</v>
-      </c>
-      <c r="K29" t="n">
-        <v>38.99007638068943</v>
-      </c>
-      <c r="L29" t="n">
-        <v>70332.00490093652</v>
-      </c>
-      <c r="M29" t="n">
-        <v>44947.60983812434</v>
-      </c>
-      <c r="N29" t="n">
-        <v>38.99007638068943</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="30">
@@ -1962,38 +1606,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F30" t="n">
+        <v>38.95660782904905</v>
+      </c>
+      <c r="G30" t="n">
+        <v>38.95660782904906</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-7.105427357601002e-15</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.65</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H30" t="n">
-        <v>126807.576212967</v>
-      </c>
-      <c r="I30" t="n">
-        <v>70332.00490093652</v>
-      </c>
       <c r="J30" t="n">
-        <v>56475.57131203044</v>
-      </c>
-      <c r="K30" t="n">
-        <v>44.53643307335404</v>
-      </c>
-      <c r="L30" t="n">
-        <v>74827.9098757599</v>
-      </c>
-      <c r="M30" t="n">
-        <v>51979.66633720706</v>
-      </c>
-      <c r="N30" t="n">
-        <v>40.99097852789949</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2014,38 +1646,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F31" t="n">
+        <v>41.30195364682256</v>
+      </c>
+      <c r="G31" t="n">
+        <v>45.53801951472652</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-4.23606586790396</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.65</v>
       </c>
-      <c r="G31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H31" t="n">
-        <v>97987.67252820171</v>
-      </c>
-      <c r="I31" t="n">
-        <v>70332.00490093652</v>
-      </c>
       <c r="J31" t="n">
-        <v>27655.6676272652</v>
-      </c>
-      <c r="K31" t="n">
-        <v>28.22361927139932</v>
-      </c>
-      <c r="L31" t="n">
-        <v>63588.14743870146</v>
-      </c>
-      <c r="M31" t="n">
-        <v>34399.52508950025</v>
-      </c>
-      <c r="N31" t="n">
-        <v>35.10597221257579</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="32">
@@ -2066,38 +1686,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F32" t="n">
+        <v>16.03811125991174</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11.12170726897754</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.916403990934198</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.55</v>
       </c>
-      <c r="G32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H32" t="n">
-        <v>27996.47786520049</v>
-      </c>
-      <c r="I32" t="n">
-        <v>17028.41177828696</v>
-      </c>
       <c r="J32" t="n">
-        <v>10968.06608691353</v>
-      </c>
-      <c r="K32" t="n">
-        <v>39.17659264041493</v>
-      </c>
-      <c r="L32" t="n">
-        <v>17028.41177828696</v>
-      </c>
-      <c r="M32" t="n">
-        <v>10968.06608691353</v>
-      </c>
-      <c r="N32" t="n">
-        <v>39.17659264041493</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="33">
@@ -2118,38 +1726,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F33" t="n">
+        <v>20.10797833106182</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20.10797833106182</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
         <v>0.55</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H33" t="n">
-        <v>30796.12565172055</v>
-      </c>
-      <c r="I33" t="n">
-        <v>17028.41177828696</v>
-      </c>
       <c r="J33" t="n">
-        <v>13767.71387343359</v>
-      </c>
-      <c r="K33" t="n">
-        <v>44.70599330946813</v>
-      </c>
-      <c r="L33" t="n">
-        <v>17952.29554783858</v>
-      </c>
-      <c r="M33" t="n">
-        <v>12843.83010388197</v>
-      </c>
-      <c r="N33" t="n">
-        <v>41.70599330946812</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2170,38 +1766,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F34" t="n">
+        <v>24.0810310634822</v>
+      </c>
+      <c r="G34" t="n">
+        <v>28.88048322454349</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-4.799452161061293</v>
+      </c>
+      <c r="I34" t="n">
         <v>0.55</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H34" t="n">
-        <v>23797.00618542042</v>
-      </c>
-      <c r="I34" t="n">
-        <v>17028.41177828696</v>
-      </c>
       <c r="J34" t="n">
-        <v>6768.594407133456</v>
-      </c>
-      <c r="K34" t="n">
-        <v>28.44305016519403</v>
-      </c>
-      <c r="L34" t="n">
-        <v>15642.58612395954</v>
-      </c>
-      <c r="M34" t="n">
-        <v>8154.420061460878</v>
-      </c>
-      <c r="N34" t="n">
-        <v>34.26657957695873</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="35">
@@ -2222,38 +1806,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F35" t="n">
+        <v>14.75703145639051</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10.23333616766366</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.523695288726852</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.55</v>
       </c>
-      <c r="G35" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H35" t="n">
-        <v>27996.47786520049</v>
-      </c>
-      <c r="I35" t="n">
-        <v>17962.12277662029</v>
-      </c>
       <c r="J35" t="n">
-        <v>10034.3550885802</v>
-      </c>
-      <c r="K35" t="n">
-        <v>35.84149097930944</v>
-      </c>
-      <c r="L35" t="n">
-        <v>17962.12277662029</v>
-      </c>
-      <c r="M35" t="n">
-        <v>10034.3550885802</v>
-      </c>
-      <c r="N35" t="n">
-        <v>35.84149097930944</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="36">
@@ -2274,38 +1846,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F36" t="n">
+        <v>18.66247287888</v>
+      </c>
+      <c r="G36" t="n">
+        <v>18.66247287888</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.55</v>
       </c>
-      <c r="G36" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H36" t="n">
-        <v>30796.12565172055</v>
-      </c>
-      <c r="I36" t="n">
-        <v>17962.12277662029</v>
-      </c>
       <c r="J36" t="n">
-        <v>12834.00287510025</v>
-      </c>
-      <c r="K36" t="n">
-        <v>41.67408270846314</v>
-      </c>
-      <c r="L36" t="n">
-        <v>18886.00654617191</v>
-      </c>
-      <c r="M36" t="n">
-        <v>11910.11910554863</v>
-      </c>
-      <c r="N36" t="n">
-        <v>38.67408270846313</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2326,38 +1886,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F37" t="n">
+        <v>22.54099698194301</v>
+      </c>
+      <c r="G37" t="n">
+        <v>27.03351378457774</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-4.492516802634725</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.55</v>
       </c>
-      <c r="G37" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H37" t="n">
-        <v>23797.00618542042</v>
-      </c>
-      <c r="I37" t="n">
-        <v>17962.12277662029</v>
-      </c>
       <c r="J37" t="n">
-        <v>5834.883408800124</v>
-      </c>
-      <c r="K37" t="n">
-        <v>24.51940115212875</v>
-      </c>
-      <c r="L37" t="n">
-        <v>16576.29712229287</v>
-      </c>
-      <c r="M37" t="n">
-        <v>7220.709063127546</v>
-      </c>
-      <c r="N37" t="n">
-        <v>30.34293056389344</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="38">
@@ -2378,38 +1926,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F38" t="n">
+        <v>9.415144314320237</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.608862776503871</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.806281537816366</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.4</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H38" t="n">
-        <v>8645.971105429564</v>
-      </c>
-      <c r="I38" t="n">
-        <v>5418.107722424405</v>
-      </c>
       <c r="J38" t="n">
-        <v>3227.863383005159</v>
-      </c>
-      <c r="K38" t="n">
-        <v>37.33372854991501</v>
-      </c>
-      <c r="L38" t="n">
-        <v>5418.107722424405</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3227.863383005159</v>
-      </c>
-      <c r="N38" t="n">
-        <v>37.33372854991501</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="39">
@@ -2430,38 +1966,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F39" t="n">
+        <v>15.16492683615157</v>
+      </c>
+      <c r="G39" t="n">
+        <v>15.16492683615157</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.4</v>
       </c>
-      <c r="G39" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H39" t="n">
-        <v>9510.568215972522</v>
-      </c>
-      <c r="I39" t="n">
-        <v>5418.107722424405</v>
-      </c>
       <c r="J39" t="n">
-        <v>4092.460493548117</v>
-      </c>
-      <c r="K39" t="n">
-        <v>43.03066231810456</v>
-      </c>
-      <c r="L39" t="n">
-        <v>5625.611028954714</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3884.957187017808</v>
-      </c>
-      <c r="N39" t="n">
-        <v>40.84884413628638</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2482,38 +2006,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F40" t="n">
+        <v>20.78134184949961</v>
+      </c>
+      <c r="G40" t="n">
+        <v>24.49933582455042</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-3.717993975050813</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.4</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H40" t="n">
-        <v>7349.075439615129</v>
-      </c>
-      <c r="I40" t="n">
-        <v>5418.107722424405</v>
-      </c>
       <c r="J40" t="n">
-        <v>1930.967717190724</v>
-      </c>
-      <c r="K40" t="n">
-        <v>26.27497476460589</v>
-      </c>
-      <c r="L40" t="n">
-        <v>5106.85276262894</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2242.222676986189</v>
-      </c>
-      <c r="N40" t="n">
-        <v>30.51026888225296</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="41">
@@ -2534,38 +2046,26 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F41" t="n">
+        <v>8.573985039914675</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.107760851157017</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.466224188757658</v>
+      </c>
+      <c r="I41" t="n">
         <v>0.4</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H41" t="n">
-        <v>8645.971105429564</v>
-      </c>
-      <c r="I41" t="n">
-        <v>6351.818720757738</v>
-      </c>
       <c r="J41" t="n">
-        <v>2294.152384671826</v>
-      </c>
-      <c r="K41" t="n">
-        <v>26.53435174252579</v>
-      </c>
-      <c r="L41" t="n">
-        <v>6351.818720757738</v>
-      </c>
-      <c r="M41" t="n">
-        <v>2294.152384671826</v>
-      </c>
-      <c r="N41" t="n">
-        <v>26.53435174252579</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="42">
@@ -2586,38 +2086,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F42" t="n">
+        <v>13.94399996139088</v>
+      </c>
+      <c r="G42" t="n">
+        <v>13.94399996139088</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>0.4</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H42" t="n">
-        <v>9510.568215972522</v>
-      </c>
-      <c r="I42" t="n">
-        <v>6351.818720757738</v>
-      </c>
       <c r="J42" t="n">
-        <v>3158.749495214784</v>
-      </c>
-      <c r="K42" t="n">
-        <v>33.21304703865982</v>
-      </c>
-      <c r="L42" t="n">
-        <v>6559.322027288048</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2951.246188684474</v>
-      </c>
-      <c r="N42" t="n">
-        <v>31.03122885684164</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2638,38 +2126,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F43" t="n">
+        <v>19.29097432807888</v>
+      </c>
+      <c r="G43" t="n">
+        <v>22.74232635549304</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-3.45135202741416</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.4</v>
       </c>
-      <c r="G43" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H43" t="n">
-        <v>7349.075439615129</v>
-      </c>
-      <c r="I43" t="n">
-        <v>6351.818720757738</v>
-      </c>
       <c r="J43" t="n">
-        <v>997.2567188573903</v>
-      </c>
-      <c r="K43" t="n">
-        <v>13.56982557944209</v>
-      </c>
-      <c r="L43" t="n">
-        <v>6040.563760962274</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1308.511678652855</v>
-      </c>
-      <c r="N43" t="n">
-        <v>17.80511969708916</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="44">
@@ -2690,38 +2166,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F44" t="n">
+        <v>10.8377270528927</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.606393770806382</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5.231333282086317</v>
+      </c>
+      <c r="I44" t="n">
         <v>0.55</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H44" t="n">
-        <v>22644.21003802981</v>
-      </c>
-      <c r="I44" t="n">
-        <v>13817.05108198455</v>
-      </c>
       <c r="J44" t="n">
-        <v>8827.158956045258</v>
-      </c>
-      <c r="K44" t="n">
-        <v>38.98196908269482</v>
-      </c>
-      <c r="L44" t="n">
-        <v>13817.05108198455</v>
-      </c>
-      <c r="M44" t="n">
-        <v>8827.158956045256</v>
-      </c>
-      <c r="N44" t="n">
-        <v>38.98196908269481</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="45">
@@ -2742,38 +2206,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F45" t="n">
+        <v>15.15896863840102</v>
+      </c>
+      <c r="G45" t="n">
+        <v>15.15896863840102</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>0.55</v>
       </c>
-      <c r="G45" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H45" t="n">
-        <v>24908.6310418328</v>
-      </c>
-      <c r="I45" t="n">
-        <v>13817.05108198455</v>
-      </c>
       <c r="J45" t="n">
-        <v>11091.57995984824</v>
-      </c>
-      <c r="K45" t="n">
-        <v>44.52906280244984</v>
-      </c>
-      <c r="L45" t="n">
-        <v>14564.31001323954</v>
-      </c>
-      <c r="M45" t="n">
-        <v>10344.32102859326</v>
-      </c>
-      <c r="N45" t="n">
-        <v>41.52906280244984</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2794,38 +2246,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F46" t="n">
+        <v>19.38037294747958</v>
+      </c>
+      <c r="G46" t="n">
+        <v>24.49084233972199</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-5.110469392242418</v>
+      </c>
+      <c r="I46" t="n">
         <v>0.55</v>
       </c>
-      <c r="G46" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H46" t="n">
-        <v>19247.57853232534</v>
-      </c>
-      <c r="I46" t="n">
-        <v>13817.05108198455</v>
-      </c>
       <c r="J46" t="n">
-        <v>5430.527450340784</v>
-      </c>
-      <c r="K46" t="n">
-        <v>28.2140812737586</v>
-      </c>
-      <c r="L46" t="n">
-        <v>12696.16268510208</v>
-      </c>
-      <c r="M46" t="n">
-        <v>6551.415847223259</v>
-      </c>
-      <c r="N46" t="n">
-        <v>34.03761068552331</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="47">
@@ -2846,38 +2286,26 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F47" t="n">
+        <v>9.853860809999404</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5.097436353024635</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.756424456974768</v>
+      </c>
+      <c r="I47" t="n">
         <v>0.55</v>
       </c>
-      <c r="G47" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H47" t="n">
-        <v>22644.21003802981</v>
-      </c>
-      <c r="I47" t="n">
-        <v>14750.76208031789</v>
-      </c>
       <c r="J47" t="n">
-        <v>7893.447957711924</v>
-      </c>
-      <c r="K47" t="n">
-        <v>34.85857066532802</v>
-      </c>
-      <c r="L47" t="n">
-        <v>14750.76208031789</v>
-      </c>
-      <c r="M47" t="n">
-        <v>7893.447957711922</v>
-      </c>
-      <c r="N47" t="n">
-        <v>34.85857066532802</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="48">
@@ -2898,38 +2326,26 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F48" t="n">
+        <v>13.91859546276631</v>
+      </c>
+      <c r="G48" t="n">
+        <v>13.91859546276631</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>0.55</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H48" t="n">
-        <v>24908.6310418328</v>
-      </c>
-      <c r="I48" t="n">
-        <v>14750.76208031789</v>
-      </c>
       <c r="J48" t="n">
-        <v>10157.86896151491</v>
-      </c>
-      <c r="K48" t="n">
-        <v>40.78051878666185</v>
-      </c>
-      <c r="L48" t="n">
-        <v>15498.02101157287</v>
-      </c>
-      <c r="M48" t="n">
-        <v>9410.610030259924</v>
-      </c>
-      <c r="N48" t="n">
-        <v>37.78051878666185</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2950,38 +2366,26 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F49" t="n">
+        <v>17.96750450099189</v>
+      </c>
+      <c r="G49" t="n">
+        <v>22.70541032231605</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-4.737905821324166</v>
+      </c>
+      <c r="I49" t="n">
         <v>0.55</v>
       </c>
-      <c r="G49" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H49" t="n">
-        <v>19247.57853232534</v>
-      </c>
-      <c r="I49" t="n">
-        <v>14750.76208031789</v>
-      </c>
       <c r="J49" t="n">
-        <v>4496.81645200745</v>
-      </c>
-      <c r="K49" t="n">
-        <v>23.36302431215061</v>
-      </c>
-      <c r="L49" t="n">
-        <v>13629.87368343541</v>
-      </c>
-      <c r="M49" t="n">
-        <v>5617.704848889925</v>
-      </c>
-      <c r="N49" t="n">
-        <v>29.18655372391531</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="50">
@@ -3002,38 +2406,26 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F50" t="n">
+        <v>6.658808038423533</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.212331797390654</v>
+      </c>
+      <c r="H50" t="n">
+        <v>5.446476241032879</v>
+      </c>
+      <c r="I50" t="n">
         <v>0.55</v>
       </c>
-      <c r="G50" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H50" t="n">
-        <v>17703.65512064149</v>
-      </c>
-      <c r="I50" t="n">
-        <v>10852.71813155156</v>
-      </c>
       <c r="J50" t="n">
-        <v>6850.936989089929</v>
-      </c>
-      <c r="K50" t="n">
-        <v>38.69786743135384</v>
-      </c>
-      <c r="L50" t="n">
-        <v>10852.71813155156</v>
-      </c>
-      <c r="M50" t="n">
-        <v>6850.936989089929</v>
-      </c>
-      <c r="N50" t="n">
-        <v>38.69786743135384</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="51">
@@ -3054,38 +2446,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F51" t="n">
+        <v>11.15605210503196</v>
+      </c>
+      <c r="G51" t="n">
+        <v>11.15605210503196</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
         <v>0.55</v>
       </c>
-      <c r="G51" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H51" t="n">
-        <v>19474.02063270564</v>
-      </c>
-      <c r="I51" t="n">
-        <v>10852.71813155156</v>
-      </c>
       <c r="J51" t="n">
-        <v>8621.302501154081</v>
-      </c>
-      <c r="K51" t="n">
-        <v>44.27078857395805</v>
-      </c>
-      <c r="L51" t="n">
-        <v>11436.93875053273</v>
-      </c>
-      <c r="M51" t="n">
-        <v>8037.081882172912</v>
-      </c>
-      <c r="N51" t="n">
-        <v>41.27078857395804</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3106,38 +2486,26 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F52" t="n">
+        <v>15.55785431226244</v>
+      </c>
+      <c r="G52" t="n">
+        <v>20.88874380465481</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-5.330889492392375</v>
+      </c>
+      <c r="I52" t="n">
         <v>0.55</v>
       </c>
-      <c r="G52" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H52" t="n">
-        <v>15048.10685254526</v>
-      </c>
-      <c r="I52" t="n">
-        <v>10852.71813155156</v>
-      </c>
       <c r="J52" t="n">
-        <v>4195.388720993704</v>
-      </c>
-      <c r="K52" t="n">
-        <v>27.87984403688687</v>
-      </c>
-      <c r="L52" t="n">
-        <v>9976.387203079805</v>
-      </c>
-      <c r="M52" t="n">
-        <v>5071.719649465458</v>
-      </c>
-      <c r="N52" t="n">
-        <v>33.70337344865158</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="53">
@@ -3158,38 +2526,26 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F53" t="n">
+        <v>5.863724318852459</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.067575368122594</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.796148950729865</v>
+      </c>
+      <c r="I53" t="n">
         <v>0.55</v>
       </c>
-      <c r="G53" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H53" t="n">
-        <v>17703.65512064149</v>
-      </c>
-      <c r="I53" t="n">
-        <v>11786.42912988489</v>
-      </c>
       <c r="J53" t="n">
-        <v>5917.225990756595</v>
-      </c>
-      <c r="K53" t="n">
-        <v>33.42375317658236</v>
-      </c>
-      <c r="L53" t="n">
-        <v>11786.42912988489</v>
-      </c>
-      <c r="M53" t="n">
-        <v>5917.225990756595</v>
-      </c>
-      <c r="N53" t="n">
-        <v>33.42375317658236</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="54">
@@ -3210,38 +2566,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F54" t="n">
+        <v>9.950628577991894</v>
+      </c>
+      <c r="G54" t="n">
+        <v>9.950628577991894</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>0.55</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H54" t="n">
-        <v>19474.02063270564</v>
-      </c>
-      <c r="I54" t="n">
-        <v>11786.42912988489</v>
-      </c>
       <c r="J54" t="n">
-        <v>7687.591502820747</v>
-      </c>
-      <c r="K54" t="n">
-        <v>39.47613925143852</v>
-      </c>
-      <c r="L54" t="n">
-        <v>12370.64974886606</v>
-      </c>
-      <c r="M54" t="n">
-        <v>7103.370883839578</v>
-      </c>
-      <c r="N54" t="n">
-        <v>36.47613925143852</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3262,38 +2606,26 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F55" t="n">
+        <v>14.05414547222039</v>
+      </c>
+      <c r="G55" t="n">
+        <v>18.86979002825418</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-4.815644556033797</v>
+      </c>
+      <c r="I55" t="n">
         <v>0.55</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H55" t="n">
-        <v>15048.10685254526</v>
-      </c>
-      <c r="I55" t="n">
-        <v>11786.42912988489</v>
-      </c>
       <c r="J55" t="n">
-        <v>3261.67772266037</v>
-      </c>
-      <c r="K55" t="n">
-        <v>21.67500373715571</v>
-      </c>
-      <c r="L55" t="n">
-        <v>10910.09820141314</v>
-      </c>
-      <c r="M55" t="n">
-        <v>4138.008651132124</v>
-      </c>
-      <c r="N55" t="n">
-        <v>27.49853314892042</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="56">
@@ -3314,38 +2646,26 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F56" t="n">
+        <v>-0.008818861735592352</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-1.622135563314508</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.613316701578916</v>
+      </c>
+      <c r="I56" t="n">
         <v>0.3</v>
       </c>
-      <c r="G56" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H56" t="n">
-        <v>11527.96147390608</v>
-      </c>
-      <c r="I56" t="n">
-        <v>7147.301943510316</v>
-      </c>
       <c r="J56" t="n">
-        <v>4380.659530395767</v>
-      </c>
-      <c r="K56" t="n">
-        <v>38.00029641243626</v>
-      </c>
-      <c r="L56" t="n">
-        <v>7147.301943510316</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4380.659530395767</v>
-      </c>
-      <c r="N56" t="n">
-        <v>38.00029641243626</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="57">
@@ -3366,38 +2686,26 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F57" t="n">
+        <v>3.973565895504098</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.973565895504098</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>0.3</v>
       </c>
-      <c r="G57" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H57" t="n">
-        <v>12680.75762129669</v>
-      </c>
-      <c r="I57" t="n">
-        <v>7147.301943510316</v>
-      </c>
       <c r="J57" t="n">
-        <v>5533.455677786378</v>
-      </c>
-      <c r="K57" t="n">
-        <v>43.63663310221479</v>
-      </c>
-      <c r="L57" t="n">
-        <v>7354.805250040625</v>
-      </c>
-      <c r="M57" t="n">
-        <v>5325.952371256069</v>
-      </c>
-      <c r="N57" t="n">
-        <v>42.00026946585116</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3418,38 +2726,26 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F58" t="n">
+        <v>8.312465341962879</v>
+      </c>
+      <c r="G58" t="n">
+        <v>10.07021085631026</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-1.757745514347379</v>
+      </c>
+      <c r="I58" t="n">
         <v>0.3</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H58" t="n">
-        <v>9798.767252820171</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7147.301943510316</v>
-      </c>
       <c r="J58" t="n">
-        <v>2651.465309309855</v>
-      </c>
-      <c r="K58" t="n">
-        <v>27.05917224992501</v>
-      </c>
-      <c r="L58" t="n">
-        <v>6836.046983714851</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2962.72026910532</v>
-      </c>
-      <c r="N58" t="n">
-        <v>30.23564283816031</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
     <row r="59">
@@ -3470,38 +2766,26 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Pesimista</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3095.585787837294</v>
+        <v>2208.516344131201</v>
       </c>
       <c r="F59" t="n">
+        <v>-0.008818861735592352</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-1.622135563314508</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.613316701578916</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.3</v>
       </c>
-      <c r="G59" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H59" t="n">
-        <v>11527.96147390608</v>
-      </c>
-      <c r="I59" t="n">
-        <v>8081.01294184365</v>
-      </c>
       <c r="J59" t="n">
-        <v>3446.948532062434</v>
-      </c>
-      <c r="K59" t="n">
-        <v>29.90076380689434</v>
-      </c>
-      <c r="L59" t="n">
-        <v>8081.01294184365</v>
-      </c>
-      <c r="M59" t="n">
-        <v>3446.948532062434</v>
-      </c>
-      <c r="N59" t="n">
-        <v>29.90076380689434</v>
+        <v>0.8901216905631737</v>
       </c>
     </row>
     <row r="60">
@@ -3522,38 +2806,26 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Optimista</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3405.144366621024</v>
+        <v>2481.139789699865</v>
       </c>
       <c r="F60" t="n">
+        <v>3.973565895504098</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.973565895504098</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.3</v>
       </c>
-      <c r="G60" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H60" t="n">
-        <v>12680.75762129669</v>
-      </c>
-      <c r="I60" t="n">
-        <v>8081.01294184365</v>
-      </c>
       <c r="J60" t="n">
-        <v>4599.744679453044</v>
-      </c>
-      <c r="K60" t="n">
-        <v>36.27342164263123</v>
-      </c>
-      <c r="L60" t="n">
-        <v>8288.516248373959</v>
-      </c>
-      <c r="M60" t="n">
-        <v>4392.241372922736</v>
-      </c>
-      <c r="N60" t="n">
-        <v>34.6370580062676</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3574,38 +2846,26 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Pesimista</t>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2631.2479196617</v>
+        <v>2819.30371598208</v>
       </c>
       <c r="F61" t="n">
+        <v>8.312465341962879</v>
+      </c>
+      <c r="G61" t="n">
+        <v>10.07021085631026</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-1.757745514347379</v>
+      </c>
+      <c r="I61" t="n">
         <v>0.3</v>
       </c>
-      <c r="G61" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H61" t="n">
-        <v>9798.767252820171</v>
-      </c>
-      <c r="I61" t="n">
-        <v>8081.01294184365</v>
-      </c>
       <c r="J61" t="n">
-        <v>1717.754310976521</v>
-      </c>
-      <c r="K61" t="n">
-        <v>17.53031036105217</v>
-      </c>
-      <c r="L61" t="n">
-        <v>7769.757982048185</v>
-      </c>
-      <c r="M61" t="n">
-        <v>2029.009270771986</v>
-      </c>
-      <c r="N61" t="n">
-        <v>20.70678094928747</v>
+        <v>1.136293782271382</v>
       </c>
     </row>
   </sheetData>
